--- a/dados_teste/Dolar.xlsx
+++ b/dados_teste/Dolar.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planilha1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -715,6 +715,96 @@
         <v>9</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>5.37</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>5.36</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>5.35</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5.33</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
 </worksheet>
